--- a/템플릿/1.표지,청구서,회보서_템플릿.xlsx
+++ b/템플릿/1.표지,청구서,회보서_템플릿.xlsx
@@ -2553,8 +2553,7 @@
       <c r="K13" s="95"/>
       <c r="L13" s="97"/>
       <c r="M13" s="98">
-        <f>+AN14</f>
-        <v>1255000</v>
+        <f>+AN15</f>
       </c>
       <c r="N13" s="98"/>
       <c r="O13" s="98"/>
